--- a/data/trans_bre/P1804_2016_2023-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1804_2016_2023-Estudios-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,25</t>
+          <t>2,86</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>51,3%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 5,96</t>
+          <t>-0,06; 6,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,64</t>
+          <t>0,36; 5,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 83,95</t>
+          <t>-0,98; 84,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 106,13</t>
+          <t>4,51; 114,47</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,75</t>
+          <t>2,05</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>38,14%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,49</t>
+          <t>1,48; 4,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 3,92</t>
+          <t>0,5; 3,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,94; 97,06</t>
+          <t>24,77; 103,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 114,73</t>
+          <t>7,22; 80,35</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>2,53</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 9,09</t>
+          <t>1,26; 9,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 5,46</t>
+          <t>-1,06; 5,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,71; 164,64</t>
+          <t>14,2; 165,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 75,32</t>
+          <t>-8,76; 75,87</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,04</t>
+          <t>2,31</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>37,28%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,96</t>
+          <t>2,3; 5,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,57</t>
+          <t>0,88; 3,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,26; 87,9</t>
+          <t>32,94; 88,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,76; 76,79</t>
+          <t>12,15; 62,35</t>
         </is>
       </c>
     </row>
